--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/GEORGIA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/GEORGIA_2015.xlsx
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C143">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C198">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C337">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C795">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C912">
@@ -16782,7 +16782,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C913">
@@ -17646,7 +17646,7 @@
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C961">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C962">
